--- a/src/result/lfw/lin_no_svd.xlsx
+++ b/src/result/lfw/lin_no_svd.xlsx
@@ -413,237 +413,182 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>f1-score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.6470588235294118</v>
       </c>
       <c r="B2" t="n">
-        <v>0.625</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6451612903225806</v>
-      </c>
-      <c r="E2" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0.8507462686567164</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8507462686567164</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8382352941176471</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8444444444444444</v>
-      </c>
-      <c r="E3" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A4" t="n">
+        <v>0.71875</v>
       </c>
       <c r="B4" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7301587301587301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.8983050847457628</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8412698412698413</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8688524590163934</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.7</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.6774193548387096</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6885245901639344</v>
-      </c>
-      <c r="E4" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8650793650793651</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.8685258964143426</v>
-      </c>
-      <c r="E5" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.7826086956521739</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E6" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7878787878787878</v>
-      </c>
-      <c r="E7" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8</v>
-      </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="E8" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A9" t="n">
+        <v>0.8043478260869565</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8409090909090909</v>
-      </c>
-      <c r="E9" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
+      <c r="A10" t="n">
+        <v>0.8249258160237388</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.8249258160237388</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.8249258160237388</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8219584569732937</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.8249258160237388</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>macro avg</t>
-        </is>
+      <c r="A11" t="n">
+        <v>0.7940676670440225</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7965117618429591</v>
+        <v>0.8147918786495429</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7951202196633679</v>
+        <v>0.8001030000683449</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7892916236277587</v>
-      </c>
-      <c r="E11" t="n">
         <v>337</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>weighted avg</t>
-        </is>
+      <c r="A12" t="n">
+        <v>0.8324778137486987</v>
       </c>
       <c r="B12" t="n">
-        <v>0.827122715027623</v>
+        <v>0.8249258160237388</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8219584569732937</v>
+        <v>0.82633665194647</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8215744541922088</v>
-      </c>
-      <c r="E12" t="n">
         <v>337</v>
       </c>
     </row>
